--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128744354</v>
+        <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>91466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622849</v>
+        <v>622764</v>
       </c>
       <c r="R2" t="n">
-        <v>7315429</v>
+        <v>7315235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128744350</v>
+        <v>128744354</v>
       </c>
       <c r="B3" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622764</v>
+        <v>622849</v>
       </c>
       <c r="R3" t="n">
-        <v>7315235</v>
+        <v>7315429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128744366</v>
+        <v>128744364</v>
       </c>
       <c r="B4" t="n">
-        <v>78492</v>
+        <v>91484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622694</v>
+        <v>622625</v>
       </c>
       <c r="R4" t="n">
-        <v>7315422</v>
+        <v>7315250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128744364</v>
+        <v>128744366</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>78492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622625</v>
+        <v>622694</v>
       </c>
       <c r="R5" t="n">
-        <v>7315250</v>
+        <v>7315422</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128744349</v>
+        <v>128744359</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>91762</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622713</v>
+        <v>622558</v>
       </c>
       <c r="R12" t="n">
-        <v>7315486</v>
+        <v>7315317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128744359</v>
+        <v>128744349</v>
       </c>
       <c r="B13" t="n">
-        <v>91762</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622558</v>
+        <v>622713</v>
       </c>
       <c r="R13" t="n">
-        <v>7315317</v>
+        <v>7315486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744356</v>
+        <v>128744348</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622695</v>
+        <v>622694</v>
       </c>
       <c r="R14" t="n">
-        <v>7315176</v>
+        <v>7315422</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744348</v>
+        <v>128744356</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622694</v>
+        <v>622695</v>
       </c>
       <c r="R15" t="n">
-        <v>7315422</v>
+        <v>7315176</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744344</v>
+        <v>128744361</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>79168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622756</v>
+        <v>622683</v>
       </c>
       <c r="R18" t="n">
-        <v>7315345</v>
+        <v>7315399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744361</v>
+        <v>128744344</v>
       </c>
       <c r="B19" t="n">
-        <v>79168</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622683</v>
+        <v>622756</v>
       </c>
       <c r="R19" t="n">
-        <v>7315399</v>
+        <v>7315345</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128744355</v>
+        <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>91466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,42 +2846,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622779</v>
+        <v>622760</v>
       </c>
       <c r="R22" t="n">
-        <v>7315243</v>
+        <v>7315219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128744351</v>
+        <v>128744355</v>
       </c>
       <c r="B23" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,34 +2953,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622760</v>
+        <v>622779</v>
       </c>
       <c r="R23" t="n">
-        <v>7315219</v>
+        <v>7315243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128744364</v>
+        <v>128744366</v>
       </c>
       <c r="B4" t="n">
-        <v>91484</v>
+        <v>78492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622625</v>
+        <v>622694</v>
       </c>
       <c r="R4" t="n">
-        <v>7315250</v>
+        <v>7315422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128744366</v>
+        <v>128744364</v>
       </c>
       <c r="B5" t="n">
-        <v>78492</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622694</v>
+        <v>622625</v>
       </c>
       <c r="R5" t="n">
-        <v>7315422</v>
+        <v>7315250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128744359</v>
+        <v>128744349</v>
       </c>
       <c r="B12" t="n">
-        <v>91762</v>
+        <v>79708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622558</v>
+        <v>622713</v>
       </c>
       <c r="R12" t="n">
-        <v>7315317</v>
+        <v>7315486</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128744349</v>
+        <v>128744359</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>91762</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622713</v>
+        <v>622558</v>
       </c>
       <c r="R13" t="n">
-        <v>7315486</v>
+        <v>7315317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128744364</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128744353</v>
+        <v>128744363</v>
       </c>
       <c r="B7" t="n">
-        <v>91466</v>
+        <v>91485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622624</v>
+        <v>622699</v>
       </c>
       <c r="R7" t="n">
-        <v>7315373</v>
+        <v>7315175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128744363</v>
+        <v>128744353</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622699</v>
+        <v>622624</v>
       </c>
       <c r="R8" t="n">
-        <v>7315175</v>
+        <v>7315373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1447,7 @@
         <v>128744358</v>
       </c>
       <c r="B9" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128744362</v>
       </c>
       <c r="B11" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128744349</v>
+        <v>128744359</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>91763</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622713</v>
+        <v>622558</v>
       </c>
       <c r="R12" t="n">
-        <v>7315486</v>
+        <v>7315317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128744359</v>
+        <v>128744349</v>
       </c>
       <c r="B13" t="n">
-        <v>91762</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622558</v>
+        <v>622713</v>
       </c>
       <c r="R13" t="n">
-        <v>7315317</v>
+        <v>7315486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128744352</v>
+        <v>128744344</v>
       </c>
       <c r="B16" t="n">
-        <v>91466</v>
+        <v>79708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622566</v>
+        <v>622756</v>
       </c>
       <c r="R16" t="n">
-        <v>7315301</v>
+        <v>7315345</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744343</v>
+        <v>128744352</v>
       </c>
       <c r="B17" t="n">
-        <v>96837</v>
+        <v>91467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622581</v>
+        <v>622566</v>
       </c>
       <c r="R17" t="n">
-        <v>7315368</v>
+        <v>7315301</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744361</v>
+        <v>128744343</v>
       </c>
       <c r="B18" t="n">
-        <v>79168</v>
+        <v>96838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622683</v>
+        <v>622581</v>
       </c>
       <c r="R18" t="n">
-        <v>7315399</v>
+        <v>7315368</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744344</v>
+        <v>128744361</v>
       </c>
       <c r="B19" t="n">
-        <v>79708</v>
+        <v>79168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622756</v>
+        <v>622683</v>
       </c>
       <c r="R19" t="n">
-        <v>7315345</v>
+        <v>7315399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2838,7 +2838,7 @@
         <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128744354</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128744366</v>
+        <v>128744364</v>
       </c>
       <c r="B4" t="n">
-        <v>78492</v>
+        <v>91512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622694</v>
+        <v>622625</v>
       </c>
       <c r="R4" t="n">
-        <v>7315422</v>
+        <v>7315250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128744364</v>
+        <v>128744366</v>
       </c>
       <c r="B5" t="n">
-        <v>91485</v>
+        <v>78519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622625</v>
+        <v>622694</v>
       </c>
       <c r="R5" t="n">
-        <v>7315250</v>
+        <v>7315422</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1114,7 @@
         <v>128744357</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128744363</v>
+        <v>128744353</v>
       </c>
       <c r="B7" t="n">
-        <v>91485</v>
+        <v>91494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622699</v>
+        <v>622624</v>
       </c>
       <c r="R7" t="n">
-        <v>7315175</v>
+        <v>7315373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128744353</v>
+        <v>128744363</v>
       </c>
       <c r="B8" t="n">
-        <v>91467</v>
+        <v>91512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622624</v>
+        <v>622699</v>
       </c>
       <c r="R8" t="n">
-        <v>7315373</v>
+        <v>7315175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1447,7 @@
         <v>128744358</v>
       </c>
       <c r="B9" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128744365</v>
       </c>
       <c r="B10" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128744362</v>
       </c>
       <c r="B11" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>128744359</v>
       </c>
       <c r="B12" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128744349</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128744348</v>
       </c>
       <c r="B14" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128744356</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128744344</v>
+        <v>128744352</v>
       </c>
       <c r="B16" t="n">
-        <v>79708</v>
+        <v>91494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622756</v>
+        <v>622566</v>
       </c>
       <c r="R16" t="n">
-        <v>7315345</v>
+        <v>7315301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744352</v>
+        <v>128744343</v>
       </c>
       <c r="B17" t="n">
-        <v>91467</v>
+        <v>96865</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622566</v>
+        <v>622581</v>
       </c>
       <c r="R17" t="n">
-        <v>7315301</v>
+        <v>7315368</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744343</v>
+        <v>128744361</v>
       </c>
       <c r="B18" t="n">
-        <v>96838</v>
+        <v>79195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622581</v>
+        <v>622683</v>
       </c>
       <c r="R18" t="n">
-        <v>7315368</v>
+        <v>7315399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744361</v>
+        <v>128744344</v>
       </c>
       <c r="B19" t="n">
-        <v>79168</v>
+        <v>79735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622683</v>
+        <v>622756</v>
       </c>
       <c r="R19" t="n">
-        <v>7315399</v>
+        <v>7315345</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>128744346</v>
       </c>
       <c r="B20" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128744347</v>
       </c>
       <c r="B21" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128744355</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128744360</v>
       </c>
       <c r="B24" t="n">
-        <v>81074</v>
+        <v>81101</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128744350</v>
+        <v>128744354</v>
       </c>
       <c r="B2" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622764</v>
+        <v>622849</v>
       </c>
       <c r="R2" t="n">
-        <v>7315235</v>
+        <v>7315429</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128744354</v>
+        <v>128744350</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>91494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622849</v>
+        <v>622764</v>
       </c>
       <c r="R3" t="n">
-        <v>7315429</v>
+        <v>7315235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128744364</v>
+        <v>128744366</v>
       </c>
       <c r="B4" t="n">
-        <v>91512</v>
+        <v>78519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622625</v>
+        <v>622694</v>
       </c>
       <c r="R4" t="n">
-        <v>7315250</v>
+        <v>7315422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128744366</v>
+        <v>128744364</v>
       </c>
       <c r="B5" t="n">
-        <v>78519</v>
+        <v>91512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622694</v>
+        <v>622625</v>
       </c>
       <c r="R5" t="n">
-        <v>7315422</v>
+        <v>7315250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128744352</v>
+        <v>128744343</v>
       </c>
       <c r="B16" t="n">
-        <v>91494</v>
+        <v>96865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622566</v>
+        <v>622581</v>
       </c>
       <c r="R16" t="n">
-        <v>7315301</v>
+        <v>7315368</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744343</v>
+        <v>128744361</v>
       </c>
       <c r="B17" t="n">
-        <v>96865</v>
+        <v>79195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622581</v>
+        <v>622683</v>
       </c>
       <c r="R17" t="n">
-        <v>7315368</v>
+        <v>7315399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744361</v>
+        <v>128744352</v>
       </c>
       <c r="B18" t="n">
-        <v>79195</v>
+        <v>91494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622683</v>
+        <v>622566</v>
       </c>
       <c r="R18" t="n">
-        <v>7315399</v>
+        <v>7315301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128744354</v>
+        <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>91499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622849</v>
+        <v>622764</v>
       </c>
       <c r="R2" t="n">
-        <v>7315429</v>
+        <v>7315235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128744350</v>
+        <v>128744354</v>
       </c>
       <c r="B3" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622764</v>
+        <v>622849</v>
       </c>
       <c r="R3" t="n">
-        <v>7315235</v>
+        <v>7315429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
         <v>128744366</v>
       </c>
       <c r="B4" t="n">
-        <v>78519</v>
+        <v>78523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128744364</v>
       </c>
       <c r="B5" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128744353</v>
+        <v>128744363</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>91517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622624</v>
+        <v>622699</v>
       </c>
       <c r="R7" t="n">
-        <v>7315373</v>
+        <v>7315175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128744363</v>
+        <v>128744353</v>
       </c>
       <c r="B8" t="n">
-        <v>91512</v>
+        <v>91499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622699</v>
+        <v>622624</v>
       </c>
       <c r="R8" t="n">
-        <v>7315175</v>
+        <v>7315373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1447,7 @@
         <v>128744358</v>
       </c>
       <c r="B9" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128744365</v>
       </c>
       <c r="B10" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128744362</v>
       </c>
       <c r="B11" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128744359</v>
+        <v>128744349</v>
       </c>
       <c r="B12" t="n">
-        <v>91790</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622558</v>
+        <v>622713</v>
       </c>
       <c r="R12" t="n">
-        <v>7315317</v>
+        <v>7315486</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128744349</v>
+        <v>128744359</v>
       </c>
       <c r="B13" t="n">
-        <v>79735</v>
+        <v>91795</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622713</v>
+        <v>622558</v>
       </c>
       <c r="R13" t="n">
-        <v>7315486</v>
+        <v>7315317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744348</v>
+        <v>128744356</v>
       </c>
       <c r="B14" t="n">
-        <v>79735</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622694</v>
+        <v>622695</v>
       </c>
       <c r="R14" t="n">
-        <v>7315422</v>
+        <v>7315176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744356</v>
+        <v>128744348</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>79739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622695</v>
+        <v>622694</v>
       </c>
       <c r="R15" t="n">
-        <v>7315176</v>
+        <v>7315422</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128744343</v>
+        <v>128744344</v>
       </c>
       <c r="B16" t="n">
-        <v>96865</v>
+        <v>79739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622581</v>
+        <v>622756</v>
       </c>
       <c r="R16" t="n">
-        <v>7315368</v>
+        <v>7315345</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744361</v>
+        <v>128744352</v>
       </c>
       <c r="B17" t="n">
-        <v>79195</v>
+        <v>91499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622683</v>
+        <v>622566</v>
       </c>
       <c r="R17" t="n">
-        <v>7315399</v>
+        <v>7315301</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744352</v>
+        <v>128744343</v>
       </c>
       <c r="B18" t="n">
-        <v>91494</v>
+        <v>96871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622566</v>
+        <v>622581</v>
       </c>
       <c r="R18" t="n">
-        <v>7315301</v>
+        <v>7315368</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744344</v>
+        <v>128744361</v>
       </c>
       <c r="B19" t="n">
-        <v>79735</v>
+        <v>79199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622756</v>
+        <v>622683</v>
       </c>
       <c r="R19" t="n">
-        <v>7315345</v>
+        <v>7315399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>128744346</v>
       </c>
       <c r="B20" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128744347</v>
       </c>
       <c r="B21" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128744360</v>
       </c>
       <c r="B24" t="n">
-        <v>81101</v>
+        <v>81105</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128744354</v>
+        <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622849</v>
+        <v>622764</v>
       </c>
       <c r="R2" t="n">
-        <v>7315429</v>
+        <v>7315235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128744350</v>
+        <v>128744354</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622764</v>
+        <v>622849</v>
       </c>
       <c r="R3" t="n">
-        <v>7315235</v>
+        <v>7315429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128744363</v>
+        <v>128744353</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>91520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622699</v>
+        <v>622624</v>
       </c>
       <c r="R7" t="n">
-        <v>7315175</v>
+        <v>7315373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128744353</v>
+        <v>128744363</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622624</v>
+        <v>622699</v>
       </c>
       <c r="R8" t="n">
-        <v>7315373</v>
+        <v>7315175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744356</v>
+        <v>128744348</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622695</v>
+        <v>622694</v>
       </c>
       <c r="R14" t="n">
-        <v>7315176</v>
+        <v>7315422</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744348</v>
+        <v>128744356</v>
       </c>
       <c r="B15" t="n">
-        <v>79653</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622694</v>
+        <v>622695</v>
       </c>
       <c r="R15" t="n">
-        <v>7315422</v>
+        <v>7315176</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128744366</v>
+        <v>128744364</v>
       </c>
       <c r="B4" t="n">
-        <v>78437</v>
+        <v>91541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622694</v>
+        <v>622625</v>
       </c>
       <c r="R4" t="n">
-        <v>7315422</v>
+        <v>7315250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128744364</v>
+        <v>128744366</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>78437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622625</v>
+        <v>622694</v>
       </c>
       <c r="R5" t="n">
-        <v>7315250</v>
+        <v>7315422</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1233,7 +1233,7 @@
         <v>128744353</v>
       </c>
       <c r="B7" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>128744363</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128744358</v>
       </c>
       <c r="B9" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128744362</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128744359</v>
       </c>
       <c r="B13" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128744343</v>
+        <v>128744352</v>
       </c>
       <c r="B16" t="n">
-        <v>96897</v>
+        <v>91523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622581</v>
+        <v>622566</v>
       </c>
       <c r="R16" t="n">
-        <v>7315368</v>
+        <v>7315301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744352</v>
+        <v>128744343</v>
       </c>
       <c r="B17" t="n">
-        <v>91520</v>
+        <v>96902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622566</v>
+        <v>622581</v>
       </c>
       <c r="R17" t="n">
-        <v>7315301</v>
+        <v>7315368</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2838,7 +2838,7 @@
         <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128744364</v>
+        <v>128744366</v>
       </c>
       <c r="B4" t="n">
-        <v>91541</v>
+        <v>78438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622625</v>
+        <v>622694</v>
       </c>
       <c r="R4" t="n">
-        <v>7315250</v>
+        <v>7315422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128744366</v>
+        <v>128744364</v>
       </c>
       <c r="B5" t="n">
-        <v>78437</v>
+        <v>91544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622694</v>
+        <v>622625</v>
       </c>
       <c r="R5" t="n">
-        <v>7315422</v>
+        <v>7315250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128744353</v>
+        <v>128744363</v>
       </c>
       <c r="B7" t="n">
-        <v>91523</v>
+        <v>91544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622624</v>
+        <v>622699</v>
       </c>
       <c r="R7" t="n">
-        <v>7315373</v>
+        <v>7315175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128744363</v>
+        <v>128744353</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622699</v>
+        <v>622624</v>
       </c>
       <c r="R8" t="n">
-        <v>7315175</v>
+        <v>7315373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,7 +1447,7 @@
         <v>128744358</v>
       </c>
       <c r="B9" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128744365</v>
       </c>
       <c r="B10" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128744362</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>128744349</v>
       </c>
       <c r="B12" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128744359</v>
       </c>
       <c r="B13" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>128744348</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128744352</v>
+        <v>128744343</v>
       </c>
       <c r="B16" t="n">
-        <v>91523</v>
+        <v>96905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622566</v>
+        <v>622581</v>
       </c>
       <c r="R16" t="n">
-        <v>7315301</v>
+        <v>7315368</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744343</v>
+        <v>128744361</v>
       </c>
       <c r="B17" t="n">
-        <v>96902</v>
+        <v>79114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622581</v>
+        <v>622683</v>
       </c>
       <c r="R17" t="n">
-        <v>7315368</v>
+        <v>7315399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744361</v>
+        <v>128744352</v>
       </c>
       <c r="B18" t="n">
-        <v>79113</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622683</v>
+        <v>622566</v>
       </c>
       <c r="R18" t="n">
-        <v>7315399</v>
+        <v>7315301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,7 +2517,7 @@
         <v>128744344</v>
       </c>
       <c r="B19" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128744346</v>
       </c>
       <c r="B20" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128744347</v>
       </c>
       <c r="B21" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128744360</v>
       </c>
       <c r="B24" t="n">
-        <v>81019</v>
+        <v>81020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744348</v>
+        <v>128744356</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622694</v>
+        <v>622695</v>
       </c>
       <c r="R14" t="n">
-        <v>7315422</v>
+        <v>7315176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744356</v>
+        <v>128744348</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622695</v>
+        <v>622694</v>
       </c>
       <c r="R15" t="n">
-        <v>7315176</v>
+        <v>7315422</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128744351</v>
+        <v>128744355</v>
       </c>
       <c r="B22" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,34 +2846,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622760</v>
+        <v>622779</v>
       </c>
       <c r="R22" t="n">
-        <v>7315219</v>
+        <v>7315243</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128744355</v>
+        <v>128744351</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,42 +2961,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622779</v>
+        <v>622760</v>
       </c>
       <c r="R23" t="n">
-        <v>7315243</v>
+        <v>7315219</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128744350</v>
+        <v>128744354</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622764</v>
+        <v>622849</v>
       </c>
       <c r="R2" t="n">
-        <v>7315235</v>
+        <v>7315429</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128744354</v>
+        <v>128744350</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622849</v>
+        <v>622764</v>
       </c>
       <c r="R3" t="n">
-        <v>7315429</v>
+        <v>7315235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128744366</v>
+        <v>128744364</v>
       </c>
       <c r="B4" t="n">
-        <v>78438</v>
+        <v>91544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622694</v>
+        <v>622625</v>
       </c>
       <c r="R4" t="n">
-        <v>7315422</v>
+        <v>7315250</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128744364</v>
+        <v>128744366</v>
       </c>
       <c r="B5" t="n">
-        <v>91544</v>
+        <v>78438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622625</v>
+        <v>622694</v>
       </c>
       <c r="R5" t="n">
-        <v>7315250</v>
+        <v>7315422</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128744363</v>
+        <v>128744353</v>
       </c>
       <c r="B7" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622699</v>
+        <v>622624</v>
       </c>
       <c r="R7" t="n">
-        <v>7315175</v>
+        <v>7315373</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128744353</v>
+        <v>128744363</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91544</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622624</v>
+        <v>622699</v>
       </c>
       <c r="R8" t="n">
-        <v>7315373</v>
+        <v>7315175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744356</v>
+        <v>128744348</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622695</v>
+        <v>622694</v>
       </c>
       <c r="R14" t="n">
-        <v>7315176</v>
+        <v>7315422</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744348</v>
+        <v>128744356</v>
       </c>
       <c r="B15" t="n">
-        <v>79654</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622694</v>
+        <v>622695</v>
       </c>
       <c r="R15" t="n">
-        <v>7315422</v>
+        <v>7315176</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744361</v>
+        <v>128744352</v>
       </c>
       <c r="B17" t="n">
-        <v>79114</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622683</v>
+        <v>622566</v>
       </c>
       <c r="R17" t="n">
-        <v>7315399</v>
+        <v>7315301</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744352</v>
+        <v>128744361</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>79114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622566</v>
+        <v>622683</v>
       </c>
       <c r="R18" t="n">
-        <v>7315301</v>
+        <v>7315399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128744355</v>
+        <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,42 +2846,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622779</v>
+        <v>622760</v>
       </c>
       <c r="R22" t="n">
-        <v>7315243</v>
+        <v>7315219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128744351</v>
+        <v>128744355</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,34 +2953,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622760</v>
+        <v>622779</v>
       </c>
       <c r="R23" t="n">
-        <v>7315219</v>
+        <v>7315243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128744354</v>
+        <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622849</v>
+        <v>622764</v>
       </c>
       <c r="R2" t="n">
-        <v>7315429</v>
+        <v>7315235</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128744350</v>
+        <v>128744354</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622764</v>
+        <v>622849</v>
       </c>
       <c r="R3" t="n">
-        <v>7315235</v>
+        <v>7315429</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128744349</v>
+        <v>128744359</v>
       </c>
       <c r="B12" t="n">
-        <v>79654</v>
+        <v>91811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622713</v>
+        <v>622558</v>
       </c>
       <c r="R12" t="n">
-        <v>7315486</v>
+        <v>7315317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128744359</v>
+        <v>128744349</v>
       </c>
       <c r="B13" t="n">
-        <v>91811</v>
+        <v>79654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622558</v>
+        <v>622713</v>
       </c>
       <c r="R13" t="n">
-        <v>7315317</v>
+        <v>7315486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744348</v>
+        <v>128744356</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622694</v>
+        <v>622695</v>
       </c>
       <c r="R14" t="n">
-        <v>7315422</v>
+        <v>7315176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744356</v>
+        <v>128744348</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>79654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622695</v>
+        <v>622694</v>
       </c>
       <c r="R15" t="n">
-        <v>7315176</v>
+        <v>7315422</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744352</v>
+        <v>128744344</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622566</v>
+        <v>622756</v>
       </c>
       <c r="R17" t="n">
-        <v>7315301</v>
+        <v>7315345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744344</v>
+        <v>128744352</v>
       </c>
       <c r="B19" t="n">
-        <v>79654</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622756</v>
+        <v>622566</v>
       </c>
       <c r="R19" t="n">
-        <v>7315345</v>
+        <v>7315301</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128744354</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128744364</v>
       </c>
       <c r="B4" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128744366</v>
       </c>
       <c r="B5" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128744357</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128744353</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>128744363</v>
       </c>
       <c r="B8" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128744358</v>
       </c>
       <c r="B9" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128744365</v>
       </c>
       <c r="B10" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128744362</v>
       </c>
       <c r="B11" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>128744359</v>
       </c>
       <c r="B12" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>128744349</v>
       </c>
       <c r="B13" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744356</v>
+        <v>128744348</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622695</v>
+        <v>622694</v>
       </c>
       <c r="R14" t="n">
-        <v>7315176</v>
+        <v>7315422</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744348</v>
+        <v>128744356</v>
       </c>
       <c r="B15" t="n">
-        <v>79654</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622694</v>
+        <v>622695</v>
       </c>
       <c r="R15" t="n">
-        <v>7315422</v>
+        <v>7315176</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,7 +2196,7 @@
         <v>128744343</v>
       </c>
       <c r="B16" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744344</v>
+        <v>128744361</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>79118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622756</v>
+        <v>622683</v>
       </c>
       <c r="R17" t="n">
-        <v>7315345</v>
+        <v>7315399</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744361</v>
+        <v>128744352</v>
       </c>
       <c r="B18" t="n">
-        <v>79114</v>
+        <v>91533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622683</v>
+        <v>622566</v>
       </c>
       <c r="R18" t="n">
-        <v>7315399</v>
+        <v>7315301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744352</v>
+        <v>128744344</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>79658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622566</v>
+        <v>622756</v>
       </c>
       <c r="R19" t="n">
-        <v>7315301</v>
+        <v>7315345</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>128744346</v>
       </c>
       <c r="B20" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128744347</v>
       </c>
       <c r="B21" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128744351</v>
+        <v>128744355</v>
       </c>
       <c r="B22" t="n">
-        <v>91526</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,34 +2846,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622760</v>
+        <v>622779</v>
       </c>
       <c r="R22" t="n">
-        <v>7315219</v>
+        <v>7315243</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128744355</v>
+        <v>128744351</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,42 +2961,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622779</v>
+        <v>622760</v>
       </c>
       <c r="R23" t="n">
-        <v>7315243</v>
+        <v>7315219</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3060,7 @@
         <v>128744360</v>
       </c>
       <c r="B24" t="n">
-        <v>81020</v>
+        <v>81024</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128744355</v>
+        <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>91533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,42 +2846,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622779</v>
+        <v>622760</v>
       </c>
       <c r="R22" t="n">
-        <v>7315243</v>
+        <v>7315219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2923,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2950,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128744351</v>
+        <v>128744355</v>
       </c>
       <c r="B23" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,34 +2953,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622760</v>
+        <v>622779</v>
       </c>
       <c r="R23" t="n">
-        <v>7315219</v>
+        <v>7315243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128744350</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128744354</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>128744364</v>
       </c>
       <c r="B4" t="n">
-        <v>91551</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128744366</v>
       </c>
       <c r="B5" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>128744357</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>128744353</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>128744363</v>
       </c>
       <c r="B8" t="n">
-        <v>91551</v>
+        <v>91560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>128744358</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>91827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>128744365</v>
       </c>
       <c r="B10" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>128744362</v>
       </c>
       <c r="B11" t="n">
-        <v>91551</v>
+        <v>91560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128744359</v>
+        <v>128744349</v>
       </c>
       <c r="B12" t="n">
-        <v>91818</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622558</v>
+        <v>622713</v>
       </c>
       <c r="R12" t="n">
-        <v>7315317</v>
+        <v>7315486</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128744349</v>
+        <v>128744359</v>
       </c>
       <c r="B13" t="n">
-        <v>79658</v>
+        <v>91827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622713</v>
+        <v>622558</v>
       </c>
       <c r="R13" t="n">
-        <v>7315486</v>
+        <v>7315317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744348</v>
+        <v>128744356</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622694</v>
+        <v>622695</v>
       </c>
       <c r="R14" t="n">
-        <v>7315422</v>
+        <v>7315176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744356</v>
+        <v>128744348</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622695</v>
+        <v>622694</v>
       </c>
       <c r="R15" t="n">
-        <v>7315176</v>
+        <v>7315422</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128744343</v>
+        <v>128744344</v>
       </c>
       <c r="B16" t="n">
-        <v>96915</v>
+        <v>79660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622581</v>
+        <v>622756</v>
       </c>
       <c r="R16" t="n">
-        <v>7315368</v>
+        <v>7315345</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744361</v>
+        <v>128744343</v>
       </c>
       <c r="B17" t="n">
-        <v>79118</v>
+        <v>96924</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622683</v>
+        <v>622581</v>
       </c>
       <c r="R17" t="n">
-        <v>7315399</v>
+        <v>7315368</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,7 +2410,7 @@
         <v>128744352</v>
       </c>
       <c r="B18" t="n">
-        <v>91533</v>
+        <v>91542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744344</v>
+        <v>128744361</v>
       </c>
       <c r="B19" t="n">
-        <v>79658</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622756</v>
+        <v>622683</v>
       </c>
       <c r="R19" t="n">
-        <v>7315345</v>
+        <v>7315399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>128744346</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128744347</v>
       </c>
       <c r="B21" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>128744351</v>
       </c>
       <c r="B22" t="n">
-        <v>91533</v>
+        <v>91542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128744355</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>128744360</v>
       </c>
       <c r="B24" t="n">
-        <v>81024</v>
+        <v>81026</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128744353</v>
+        <v>128744363</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>91560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622624</v>
+        <v>622699</v>
       </c>
       <c r="R7" t="n">
-        <v>7315373</v>
+        <v>7315175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128744363</v>
+        <v>128744353</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622699</v>
+        <v>622624</v>
       </c>
       <c r="R8" t="n">
-        <v>7315175</v>
+        <v>7315373</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128744349</v>
+        <v>128744359</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>91827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622713</v>
+        <v>622558</v>
       </c>
       <c r="R12" t="n">
-        <v>7315486</v>
+        <v>7315317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128744359</v>
+        <v>128744349</v>
       </c>
       <c r="B13" t="n">
-        <v>91827</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622558</v>
+        <v>622713</v>
       </c>
       <c r="R13" t="n">
-        <v>7315317</v>
+        <v>7315486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744352</v>
+        <v>128744361</v>
       </c>
       <c r="B18" t="n">
-        <v>91542</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622566</v>
+        <v>622683</v>
       </c>
       <c r="R18" t="n">
-        <v>7315301</v>
+        <v>7315399</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744361</v>
+        <v>128744352</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622683</v>
+        <v>622566</v>
       </c>
       <c r="R19" t="n">
-        <v>7315399</v>
+        <v>7315301</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128744351</v>
+        <v>128744355</v>
       </c>
       <c r="B22" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,34 +2846,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622760</v>
+        <v>622779</v>
       </c>
       <c r="R22" t="n">
-        <v>7315219</v>
+        <v>7315243</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2913,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2923,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2950,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128744355</v>
+        <v>128744351</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,42 +2961,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622779</v>
+        <v>622760</v>
       </c>
       <c r="R23" t="n">
-        <v>7315243</v>
+        <v>7315219</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128744350</v>
+        <v>128744343</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622764</v>
+        <v>622581</v>
       </c>
       <c r="R2" t="n">
-        <v>7315235</v>
+        <v>7315368</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128744354</v>
+        <v>128744365</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622849</v>
+        <v>622764</v>
       </c>
       <c r="R3" t="n">
-        <v>7315429</v>
+        <v>7315299</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128744364</v>
+        <v>128744358</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622625</v>
+        <v>622622</v>
       </c>
       <c r="R4" t="n">
-        <v>7315250</v>
+        <v>7315376</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128744366</v>
+        <v>128744359</v>
       </c>
       <c r="B5" t="n">
-        <v>78444</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622694</v>
+        <v>622558</v>
       </c>
       <c r="R5" t="n">
-        <v>7315422</v>
+        <v>7315317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128744357</v>
+        <v>128744361</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,46 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622713</v>
+        <v>622683</v>
       </c>
       <c r="R6" t="n">
-        <v>7315486</v>
+        <v>7315399</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128744363</v>
+        <v>128744360</v>
       </c>
       <c r="B7" t="n">
-        <v>91560</v>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622699</v>
+        <v>622720</v>
       </c>
       <c r="R7" t="n">
-        <v>7315175</v>
+        <v>7315492</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128744353</v>
+        <v>128744350</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622624</v>
+        <v>622764</v>
       </c>
       <c r="R8" t="n">
-        <v>7315373</v>
+        <v>7315235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128744358</v>
+        <v>128744351</v>
       </c>
       <c r="B9" t="n">
-        <v>91827</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622622</v>
+        <v>622760</v>
       </c>
       <c r="R9" t="n">
-        <v>7315376</v>
+        <v>7315219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128744365</v>
+        <v>128744352</v>
       </c>
       <c r="B10" t="n">
-        <v>78707</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622764</v>
+        <v>622566</v>
       </c>
       <c r="R10" t="n">
-        <v>7315299</v>
+        <v>7315301</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128744362</v>
+        <v>128744353</v>
       </c>
       <c r="B11" t="n">
-        <v>91560</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622795</v>
+        <v>622624</v>
       </c>
       <c r="R11" t="n">
-        <v>7315504</v>
+        <v>7315373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128744359</v>
+        <v>128744366</v>
       </c>
       <c r="B12" t="n">
-        <v>91827</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622558</v>
+        <v>622694</v>
       </c>
       <c r="R12" t="n">
-        <v>7315317</v>
+        <v>7315422</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128744349</v>
+        <v>128744344</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622713</v>
+        <v>622756</v>
       </c>
       <c r="R13" t="n">
-        <v>7315486</v>
+        <v>7315345</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128744356</v>
+        <v>128744346</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622695</v>
+        <v>622658</v>
       </c>
       <c r="R14" t="n">
-        <v>7315176</v>
+        <v>7315261</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128744348</v>
+        <v>128744347</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622694</v>
+        <v>622603</v>
       </c>
       <c r="R15" t="n">
-        <v>7315422</v>
+        <v>7315290</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128744344</v>
+        <v>128744348</v>
       </c>
       <c r="B16" t="n">
-        <v>79660</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622756</v>
+        <v>622694</v>
       </c>
       <c r="R16" t="n">
-        <v>7315345</v>
+        <v>7315422</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128744343</v>
+        <v>128744349</v>
       </c>
       <c r="B17" t="n">
-        <v>96924</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622581</v>
+        <v>622713</v>
       </c>
       <c r="R17" t="n">
-        <v>7315368</v>
+        <v>7315486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128744361</v>
+        <v>128744354</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,34 +2398,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622683</v>
+        <v>622849</v>
       </c>
       <c r="R18" t="n">
-        <v>7315399</v>
+        <v>7315429</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2465,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2475,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128744352</v>
+        <v>128744355</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,34 +2513,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622566</v>
+        <v>622779</v>
       </c>
       <c r="R19" t="n">
-        <v>7315301</v>
+        <v>7315243</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2580,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2590,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128744346</v>
+        <v>128744356</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,21 +2628,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622658</v>
+        <v>622695</v>
       </c>
       <c r="R20" t="n">
-        <v>7315261</v>
+        <v>7315176</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,7 +2687,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2697,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128744347</v>
+        <v>128744357</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,34 +2735,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långudden, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>622603</v>
+        <v>622713</v>
       </c>
       <c r="R21" t="n">
-        <v>7315290</v>
+        <v>7315486</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2832,335 +2840,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>128744355</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57727</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Långudden, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>622779</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7315243</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>128744351</v>
-      </c>
-      <c r="B23" t="n">
-        <v>91542</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Långudden, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>622760</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7315219</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>128744360</v>
-      </c>
-      <c r="B24" t="n">
-        <v>81026</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Microcalicium ahlneri</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Långudden, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>622720</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7315492</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45417-2024 artfynd.xlsx
+++ b/artfynd/A 45417-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744343</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744365</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744358</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744359</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744361</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744360</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744350</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744351</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744352</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744353</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744366</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744344</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744346</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744347</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744348</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744349</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2499,6 +2584,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744354</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2614,6 +2704,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744355</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2721,6 +2816,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744356</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2840,8 +2940,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128744357</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>